--- a/etudecas/donnees/Stocks_MRP.xlsx
+++ b/etudecas/donnees/Stocks_MRP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Varan\Echange\Data_Sources_BU_Operations\Excellence\Use_Cases_Data_Analytics\Scan3\IN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\lca-simu\etudecas\donnees\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FBF16A-1B61-4B12-B537-AABF985A1B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99D3218-7A4D-4A15-AC70-751017E73B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C5733493-3060-4324-91F7-11B73740A907}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{C5733493-3060-4324-91F7-11B73740A907}"/>
   </bookViews>
   <sheets>
     <sheet name="Stocks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="51">
   <si>
     <t>Numéro d'article</t>
   </si>
@@ -565,15 +565,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5678449-D0B1-4410-BBEF-68E8978594E7}">
   <dimension ref="A1:G51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.6328125" customWidth="1"/>
-    <col min="7" max="7" width="17.453125" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -596,7 +596,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -619,7 +619,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -642,7 +642,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
@@ -665,7 +665,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -688,7 +688,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -711,7 +711,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -734,7 +734,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -757,7 +757,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -780,7 +780,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -803,7 +803,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
@@ -826,7 +826,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -849,7 +849,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -872,7 +872,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>22</v>
       </c>
@@ -895,7 +895,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
@@ -918,7 +918,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
@@ -941,7 +941,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
@@ -964,7 +964,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>26</v>
       </c>
@@ -987,7 +987,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>27</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>35</v>
       </c>
@@ -1033,7 +1033,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>35</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>30</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>31</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>32</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>33</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>34</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>36</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>37</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>38</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>39</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>39</v>
       </c>
@@ -1286,7 +1286,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>28</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>29</v>
       </c>
@@ -1332,55 +1332,55 @@
         <v>45658.127638888887</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G35" s="1"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G38" s="1"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G40" s="1"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G44" s="1"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G45" s="1"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G46" s="1"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="7:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="7:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="7:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G51" s="1"/>
     </row>
   </sheetData>
@@ -1391,16 +1391,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7630011D-C52C-4BD0-AD3B-4E711DF92044}">
-  <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.90625" style="2"/>
-    <col min="3" max="3" width="17.36328125" customWidth="1"/>
-    <col min="4" max="4" width="21.36328125" customWidth="1"/>
-    <col min="5" max="5" width="15.08984375" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" style="2"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
@@ -1630,7 +1630,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>26</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>35</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>30</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>31</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>33</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>34</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>36</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>37</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>38</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>39</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>28</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>29</v>
       </c>
@@ -1996,6 +1996,26 @@
       </c>
       <c r="G26" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27">
+        <v>1450</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27">
+        <v>900000</v>
+      </c>
+      <c r="G27" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2006,13 +2026,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51A18ED7-4649-468F-BDA0-E4613F2DB201}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2035,7 +2055,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>268091</v>
       </c>
@@ -2058,7 +2078,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>268967</v>
       </c>
@@ -2081,7 +2101,7 @@
         <v>107800</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>773474</v>
       </c>
@@ -2111,6 +2131,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="911fa86e-1244-486f-9d05-850c48c46759">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002D5C0BAE13F791428A2467AD4E2CA4A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="2ef8d77b566c9fd80e9c2bdc9338d629">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="911fa86e-1244-486f-9d05-850c48c46759" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="803aa259af1a7fc7d7bef2888f2078ba" ns2:_="">
     <xsd:import namespace="911fa86e-1244-486f-9d05-850c48c46759"/>
@@ -2274,33 +2313,38 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="911fa86e-1244-486f-9d05-850c48c46759">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE4693B2-416D-427E-91B7-EF9C18FC3A74}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010A6EAB-D310-4612-B6AD-3FA5C652914D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="911fa86e-1244-486f-9d05-850c48c46759"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C182FF-C1A6-46B6-8461-3FF0FCC22939}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C182FF-C1A6-46B6-8461-3FF0FCC22939}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010A6EAB-D310-4612-B6AD-3FA5C652914D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE4693B2-416D-427E-91B7-EF9C18FC3A74}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="911fa86e-1244-486f-9d05-850c48c46759"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>